--- a/resultados/facturas_lubrisol.xlsx
+++ b/resultados/facturas_lubrisol.xlsx
@@ -1,40 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BU\Trabajo Andres\scriptLubrisol\siigoScript\resultados\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A819CD37-ACED-4BDD-BF23-A597851F9230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+  <si>
+    <t>FV</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Productos</t>
+  </si>
+  <si>
+    <t>BE8406</t>
+  </si>
+  <si>
+    <t>INCOLMAT SAS</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>LUBSYNT BLK Fluido sintético para mecanizado 1/5 Gal (19 litros)</t>
+  </si>
+  <si>
+    <t>BE8405</t>
+  </si>
+  <si>
+    <t>IGNACIO GOMEZ IHM SAS</t>
+  </si>
+  <si>
+    <t>BE1244</t>
+  </si>
+  <si>
+    <t>MOTO STORE DLM S</t>
+  </si>
+  <si>
+    <t>LUBSYNT BLK 1/4 Galon</t>
+  </si>
+  <si>
+    <t>BE1243</t>
+  </si>
+  <si>
+    <t>INGENIERIA METALMECANICA MALDONADO LTDA</t>
+  </si>
+  <si>
+    <t>SULFOMET C 1 Gal.</t>
+  </si>
+  <si>
+    <t>BE569</t>
+  </si>
+  <si>
+    <t>C U CONECTORES S.</t>
+  </si>
+  <si>
+    <t>EMULSOL 40 1 Gal.</t>
+  </si>
+  <si>
+    <t>BE568</t>
+  </si>
+  <si>
+    <t>BE567</t>
+  </si>
+  <si>
+    <t>ANGEL RAUL RINCON ROJAS</t>
+  </si>
+  <si>
+    <t>BE566</t>
+  </si>
+  <si>
+    <t>TECNI HIDRAULICA RINCON S.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +157,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="3">
+    <cellStyle name="40% - Énfasis5" xfId="2" builtinId="47"/>
+    <cellStyle name="Énfasis5" xfId="1" builtinId="45"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,14 +493,199 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>8406</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1245245.1299999999</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>8405</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1913700</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1244</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>35900</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>1243</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6">
+        <v>99100</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>569</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6">
+        <v>112800</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>568</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="6">
+        <v>112800</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>567</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>35900</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>566</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6">
+        <v>35900</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>